--- a/export-template.xlsx
+++ b/export-template.xlsx
@@ -23,7 +23,7 @@
     <definedName name="SAYURI_SHARE">'Summary'!$B$19</definedName>
     <definedName name="NET_LABEL">'Summary'!$A$22</definedName>
     <definedName name="NET_AMOUNT">'Summary'!$B$22</definedName>
-    <definedName name="RECURRING_TOT">'Summary'!$B$25</definedName>
+    <definedName name="REC_START">'Summary'!$A$25</definedName>
     <definedName name="CAT_TABLE">'Summary'!$C$5:$D$14</definedName>
     <definedName name="EXP_DATA">'Expenses'!$A$3:$H$1000</definedName>
     <definedName name="REC_DATA">'Recurring'!$A$3:$H$1000</definedName>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1169,14 +1169,6 @@
           <t>🔁  RECURRING (reference only — not in spend total)</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Monthly recurring total</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/export-template.xlsx
+++ b/export-template.xlsx
@@ -12,33 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="PERIOD">'Summary'!$A$2</definedName>
-    <definedName name="KENNY_INCOME">'Summary'!$B$5</definedName>
-    <definedName name="SAYURI_INCOME">'Summary'!$B$6</definedName>
-    <definedName name="TOTAL_SPENT">'Summary'!$B$10</definedName>
-    <definedName name="KENNY_PAID">'Summary'!$B$14</definedName>
-    <definedName name="SAYURI_PAID">'Summary'!$B$15</definedName>
-    <definedName name="KENNY_SHARE">'Summary'!$B$18</definedName>
-    <definedName name="SAYURI_SHARE">'Summary'!$B$19</definedName>
-    <definedName name="NET_LABEL">'Summary'!$A$22</definedName>
-    <definedName name="NET_AMOUNT">'Summary'!$B$22</definedName>
-    <definedName name="REC_START">'Summary'!$A$25</definedName>
-    <definedName name="CAT_TABLE">'Summary'!$C$5:$D$14</definedName>
-    <definedName name="EXP_DATA">'Expenses'!$A$3:$H$1000</definedName>
-    <definedName name="REC_DATA">'Recurring'!$A$3:$H$1000</definedName>
-    <definedName name="CHART_CATS">'ChartData'!$A$2:$B$11</definedName>
-    <definedName name="CHART_PERSONS">'ChartData'!$D$2:$F$3</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -48,54 +29,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000B4D8"/>
-      <sz val="12"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <color rgb="001A202C"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A202C"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0021A05A"/>
+      <color rgb="001F9D55"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -104,52 +85,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A2E"/>
+        <fgColor rgb="001A2540"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0016213E"/>
+        <fgColor rgb="00EDF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F3460"/>
+        <fgColor rgb="002C5282"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
+        <fgColor rgb="000891B2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007D3C98"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A5276"/>
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0021A05A"/>
+        <fgColor rgb="00C53030"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00145A32"/>
+        <fgColor rgb="00805AD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007F8C8D"/>
+        <fgColor rgb="00319795"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4F8"/>
+        <fgColor rgb="001F9D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001C7C41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00718096"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,64 +179,75 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -361,7 +363,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E84393"/>
+                <a:srgbClr val="2C5282"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -372,7 +374,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9B59B6"/>
+                <a:srgbClr val="DB2777"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -383,7 +385,7 @@
             <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3498DB"/>
+                <a:srgbClr val="0891B2"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -405,7 +407,7 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1ABC9C"/>
+                <a:srgbClr val="1F9D55"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -416,7 +418,7 @@
             <idx val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E74C3C"/>
+                <a:srgbClr val="C53030"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -427,7 +429,7 @@
             <idx val="6"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="F39C12"/>
+                <a:srgbClr val="D69E2E"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -438,7 +440,7 @@
             <idx val="7"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2ECC71"/>
+                <a:srgbClr val="805AD5"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -449,7 +451,7 @@
             <idx val="8"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00B4D8"/>
+                <a:srgbClr val="319795"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -460,7 +462,7 @@
             <idx val="9"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="95A5A6"/>
+                <a:srgbClr val="A0AEC0"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -469,18 +471,16 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$2:$A$11</f>
+              <f>'ChartData'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$B$2:$B$11</f>
+              <f>'ChartData'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <showCatName val="1"/>
-          <showSerName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -528,7 +528,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="00B4D8"/>
+              <a:srgbClr val="0891B2"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -555,7 +555,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="E94560"/>
+              <a:srgbClr val="DB2777"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -582,21 +582,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Person</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -647,7 +632,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3600000"/>
+    <ext cx="4680000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -666,10 +651,10 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3600000"/>
+    <ext cx="4680000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -976,47 +961,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>💰 NotBeerGoggles — Monthly Close</t>
+          <t>NotBeerGoggles — Monthly Close</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>__PERIOD__</t>
+          <t>Period</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>📥  INCOME / INFLOW</t>
+          <t>INCOME / INFLOW</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>CATEGORY BREAKDOWN</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Amount (SGD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Kenny</t>
@@ -1024,162 +1004,693 @@
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="6" t="n"/>
-    </row>
-    <row r="6">
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Sayuri</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Total Household Income</t>
         </is>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="12">
         <f>B5+B6</f>
         <v/>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="6" t="n"/>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>💸  EXPENSES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10">
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Total Spent</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Surplus / (Deficit)</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="14">
         <f>B7-B10</f>
         <v/>
       </c>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>💳  CARD PAYMENTS</t>
+          <t>CARD PAYMENTS</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="6" t="n"/>
-    </row>
-    <row r="14">
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Kenny paid (card)</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="6" t="n"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Sayuri paid (card)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>SHARE / LIABILITY</t>
         </is>
       </c>
-      <c r="D15" s="14">
-        <f>SUM(D5:D14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>⚖️  SHARE / LIABILITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Kenny's share</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Sayuri's share</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>🏦  NET SETTLEMENT</t>
+          <t>NET SETTLEMENT</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>__NET_LABEL__</t>
+          <t>Net Label</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>🔁  RECURRING (reference only — not in spend total)</t>
+          <t>TOTAL</t>
         </is>
       </c>
+      <c r="D25" s="21">
+        <f>SUM(D5:D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>RECURRING (reference — not in spend total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n"/>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="9" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n"/>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n"/>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="9" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n"/>
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="9" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n"/>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="9" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n"/>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="10" t="n"/>
+      <c r="C125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="10" t="n"/>
+      <c r="C127" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1192,74 +1703,1567 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>Amount (SGD)</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>Paid By</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>Kenny Share</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>Sayuri Share</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>Split Type</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>__EXP_PLACEHOLDER__</t>
-        </is>
-      </c>
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
+      <c r="H65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n"/>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n"/>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n"/>
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n"/>
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n"/>
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="8" t="n"/>
+      <c r="H113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n"/>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+      <c r="H117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="9" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n"/>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
+      <c r="H119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="9" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="n"/>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="8" t="n"/>
+      <c r="G121" s="8" t="n"/>
+      <c r="H121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="9" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="n"/>
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="8" t="n"/>
+      <c r="H123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="9" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="n"/>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="n"/>
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="7" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="8" t="n"/>
+      <c r="G127" s="8" t="n"/>
+      <c r="H127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="9" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="n"/>
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="7" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="8" t="n"/>
+      <c r="H129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="9" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="n"/>
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="n"/>
+      <c r="H131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="9" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="n"/>
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="7" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="8" t="n"/>
+      <c r="G133" s="8" t="n"/>
+      <c r="H133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="9" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="n"/>
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="7" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="7" t="n"/>
+      <c r="F135" s="8" t="n"/>
+      <c r="G135" s="8" t="n"/>
+      <c r="H135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="9" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="9" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="n"/>
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="7" t="n"/>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="7" t="n"/>
+      <c r="F137" s="8" t="n"/>
+      <c r="G137" s="8" t="n"/>
+      <c r="H137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="9" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="8" t="n"/>
+      <c r="G139" s="8" t="n"/>
+      <c r="H139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="9" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="n"/>
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="7" t="n"/>
+      <c r="F141" s="8" t="n"/>
+      <c r="G141" s="8" t="n"/>
+      <c r="H141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="9" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="n"/>
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="7" t="n"/>
+      <c r="F143" s="8" t="n"/>
+      <c r="G143" s="8" t="n"/>
+      <c r="H143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="9" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="n"/>
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="7" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="7" t="n"/>
+      <c r="F145" s="8" t="n"/>
+      <c r="G145" s="8" t="n"/>
+      <c r="H145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="9" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="n"/>
+      <c r="B147" s="7" t="n"/>
+      <c r="C147" s="7" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="7" t="n"/>
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="8" t="n"/>
+      <c r="H147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="10" t="n"/>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="10" t="n"/>
+      <c r="H148" s="9" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="n"/>
+      <c r="B149" s="7" t="n"/>
+      <c r="C149" s="7" t="n"/>
+      <c r="D149" s="8" t="n"/>
+      <c r="E149" s="7" t="n"/>
+      <c r="F149" s="8" t="n"/>
+      <c r="G149" s="8" t="n"/>
+      <c r="H149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="n"/>
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="10" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="10" t="n"/>
+      <c r="G150" s="10" t="n"/>
+      <c r="H150" s="9" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="n"/>
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="7" t="n"/>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="8" t="n"/>
+      <c r="G151" s="8" t="n"/>
+      <c r="H151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="10" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="10" t="n"/>
+      <c r="G152" s="10" t="n"/>
+      <c r="H152" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1275,74 +3279,1067 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>Recurring Templates (reference — not included in spend totals)</t>
+          <t>Recurring Templates (reference — not in spend totals)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Amount (SGD)</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Paid By</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Kenny Share</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>Sayuri Share</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>Split Type</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>__REC_PLACEHOLDER__</t>
-        </is>
-      </c>
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
+      <c r="H65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1358,164 +4355,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="27" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>__CAT1__</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B2" s="28" t="n"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Kenny</t>
         </is>
       </c>
-      <c r="E2" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" s="28" t="n"/>
+      <c r="F2" s="28" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>__CAT2__</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" s="28" t="n"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Sayuri</t>
         </is>
       </c>
-      <c r="E3" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>__CAT3__</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>__CAT4__</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>__CAT5__</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>__CAT6__</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>__CAT7__</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>__CAT8__</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>__CAT9__</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>__CAT10__</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" s="28" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/export-template.xlsx
+++ b/export-template.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recurring" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budgets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holiday Fund" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -170,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,6 +250,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4469,4 +4480,272 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Budgets (fixed monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY INCOME BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="26" t="inlineStr"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Sayuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Budgeted income</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CATEGORY BUDGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Sayuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Holiday Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Debt target</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Contributed</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Left to settle</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>